--- a/data/trans_dic/IP28_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP28_R-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura</t>
+          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura (tasa de respuesta: 94,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,96</t>
+          <t>0,0; 2,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,78</t>
+          <t>0,0; 3,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,65</t>
+          <t>0,0; 2,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,03</t>
+          <t>0,48; 4,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,65</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,94</t>
+          <t>0,0; 2,21</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,75</t>
+          <t>0,49; 2,72</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,85</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,13</t>
+          <t>0,31; 3,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,93</t>
+          <t>0,0; 2,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,51</t>
+          <t>0,3; 2,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,43</t>
+          <t>0,0; 0,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,82</t>
+          <t>0,0; 2,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 1,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,46</t>
+          <t>0,0; 2,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,84</t>
+          <t>0,32; 1,75</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,44</t>
+          <t>0,15; 1,45</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,47</t>
+          <t>0,16; 1,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 1,44</t>
+          <t>0,05; 1,41</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,58</t>
+          <t>0,51; 4,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 6,57</t>
+          <t>1,41; 6,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,43</t>
+          <t>0,78; 4,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>0,0; 2,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,13</t>
+          <t>0,48; 4,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,56</t>
+          <t>0,44; 4,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,81</t>
+          <t>0,39; 3,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,62</t>
+          <t>0,0; 2,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,07</t>
+          <t>0,52; 3,1</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,51</t>
+          <t>1,38; 4,63</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,42</t>
+          <t>0,8; 3,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,68</t>
+          <t>0,19; 1,67</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,72</t>
+          <t>0,65; 3,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 7,5</t>
+          <t>1,85; 7,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,73</t>
+          <t>0,0; 2,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 5,87</t>
+          <t>1,49; 5,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,58</t>
+          <t>0,94; 4,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 6,02</t>
+          <t>1,41; 5,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,73</t>
+          <t>0,47; 4,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,29</t>
+          <t>0,58; 3,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,29</t>
+          <t>1,1; 3,35</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,06; 5,66</t>
+          <t>2,03; 5,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,91</t>
+          <t>0,61; 2,83</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,71</t>
+          <t>1,3; 3,67</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,17</t>
+          <t>0,72; 2,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,03</t>
+          <t>1,16; 3,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,81</t>
+          <t>0,5; 1,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,56</t>
+          <t>0,78; 2,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,99</t>
+          <t>0,66; 2,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,63</t>
+          <t>0,99; 2,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,73</t>
+          <t>0,49; 1,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,78</t>
+          <t>0,49; 1,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,81</t>
+          <t>0,83; 1,82</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,59</t>
+          <t>1,33; 2,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,55</t>
+          <t>0,62; 1,51</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,78</t>
+          <t>0,77; 1,78</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura (tasa de respuesta: 94,73%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1236</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3444</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2748</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4990</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3217</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>635; 5482</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4950</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1297; 7169</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2991</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1751</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1359</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1455</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>4350</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2211</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2417</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1467</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>779; 7490</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4341</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>564; 4676</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 826</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4311</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4997</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3362</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3982</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1612; 8736</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>703; 6588</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>660; 5977</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>163; 4803</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4805</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3409</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2075</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2665</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2594</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1579</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>7470</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>6003</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2389</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>643; 5385</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2077; 9594</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1301; 7237</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4042</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>664; 6215</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>648; 6625</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>654; 6497</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5542</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1376; 8251</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>4088; 13669</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2694; 11418</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>712; 6432</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>3214</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6047</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1211</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8568</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4738</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5300</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3402</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>4571</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>7952</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>11346</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4614</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>13139</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1250; 7132</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2886; 11479</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4148</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>4074; 15403</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1927; 9455</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2356; 9890</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>747; 7289</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1752; 10074</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>4390; 13336</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>6566; 18062</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>1936; 8983</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>7483; 21213</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>8832</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>13052</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6372</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>9542</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>8810</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>11419</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>6661</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>7453</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>17642</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>24471</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>13033</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>16995</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>4849; 15464</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7527; 20054</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3196; 11478</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5190; 17119</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4692; 14804</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>6807; 17821</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3251; 11437</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>3703; 13771</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>11499; 25294</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>17707; 33627</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>8073; 19699</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>10908; 25233</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP28_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP28_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura (tasa de respuesta: 94,73%)</t>
+          <t>Menores cuyo peso es bastante mayor de lo normal en relación con su altura (tasa de respuesta: 94,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,66</t>
+          <t>0,0; 2,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,79</t>
+          <t>0,0; 3,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,68</t>
+          <t>0,0; 3,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,16</t>
+          <t>0,48; 4,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -757,12 +757,12 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,21</t>
+          <t>0,0; 1,91</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,72</t>
+          <t>0,49; 2,91</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -857,17 +857,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,02</t>
+          <t>0,32; 2,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,06</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,48</t>
+          <t>0,3; 2,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -877,42 +877,42 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,72</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,06</t>
+          <t>0,0; 2,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,5</t>
+          <t>0,0; 1,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,19</t>
+          <t>0,0; 3,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,75</t>
+          <t>0,36; 2,0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,45</t>
+          <t>0,16; 1,3</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,45</t>
+          <t>0,15; 1,46</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 1,41</t>
+          <t>0,09; 1,34</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,24</t>
+          <t>0,5; 4,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 6,49</t>
+          <t>1,41; 6,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,33</t>
+          <t>0,76; 4,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,36</t>
+          <t>0,0; 2,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,47</t>
+          <t>0,48; 3,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,49</t>
+          <t>0,51; 4,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,86</t>
+          <t>0,38; 3,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,61</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,1</t>
+          <t>0,75; 3,33</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,63</t>
+          <t>1,35; 4,24</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,4</t>
+          <t>0,8; 3,38</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,67</t>
+          <t>0,18; 1,71</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,71</t>
+          <t>0,66; 3,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 7,37</t>
+          <t>1,77; 6,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,65</t>
+          <t>0,0; 2,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 5,62</t>
+          <t>1,44; 5,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,59</t>
+          <t>1,01; 4,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 5,92</t>
+          <t>1,48; 6,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,54</t>
+          <t>0,83; 4,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,32</t>
+          <t>0,55; 3,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,35</t>
+          <t>1,03; 3,56</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 5,6</t>
+          <t>2,15; 5,61</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,83</t>
+          <t>0,61; 2,95</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,67</t>
+          <t>1,37; 3,82</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,31</t>
+          <t>0,73; 2,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,1</t>
+          <t>1,28; 3,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,81</t>
+          <t>0,51; 1,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,58</t>
+          <t>0,76; 2,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,07</t>
+          <t>0,68; 2,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,59</t>
+          <t>1,01; 2,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,71</t>
+          <t>0,49; 1,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,82</t>
+          <t>0,49; 1,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,82</t>
+          <t>0,86; 1,83</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,52</t>
+          <t>1,28; 2,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,51</t>
+          <t>0,63; 1,55</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,78</t>
+          <t>0,74; 1,83</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura (tasa de respuesta: 94,73%)</t>
+          <t>Menores cuyo peso es bastante mayor de lo normal en relación con su altura (tasa de respuesta: 94,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2748</t>
+          <t>0; 3001</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4990</t>
+          <t>0; 4370</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1665,12 +1665,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3217</t>
+          <t>0; 3645</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>635; 5482</t>
+          <t>638; 5405</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1685,12 +1685,12 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4950</t>
+          <t>0; 4274</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1297; 7169</t>
+          <t>1288; 7661</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>779; 7490</t>
+          <t>783; 7211</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4341</t>
+          <t>0; 4122</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>564; 4676</t>
+          <t>565; 4720</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 826</t>
+          <t>0; 829</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4311</t>
+          <t>0; 4805</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4997</t>
+          <t>0; 5361</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3362</t>
+          <t>0; 3985</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3982</t>
+          <t>0; 5480</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1612; 8736</t>
+          <t>1786; 9945</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>703; 6588</t>
+          <t>706; 5893</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>660; 5977</t>
+          <t>602; 6015</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>163; 4803</t>
+          <t>320; 4587</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>643; 5385</t>
+          <t>641; 5480</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2077; 9594</t>
+          <t>2089; 9121</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1301; 7237</t>
+          <t>1265; 6931</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4042</t>
+          <t>0; 4547</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>664; 6215</t>
+          <t>663; 5543</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>648; 6625</t>
+          <t>755; 6595</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>654; 6497</t>
+          <t>648; 5929</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 5542</t>
+          <t>0; 5092</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1376; 8251</t>
+          <t>1998; 8864</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4088; 13669</t>
+          <t>3978; 12537</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2694; 11418</t>
+          <t>2670; 11345</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>712; 6432</t>
+          <t>695; 6581</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1250; 7132</t>
+          <t>1265; 7108</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2886; 11479</t>
+          <t>2764; 10770</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4148</t>
+          <t>0; 4447</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4074; 15403</t>
+          <t>3939; 14780</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1927; 9455</t>
+          <t>2077; 9245</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2356; 9890</t>
+          <t>2465; 10169</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>747; 7289</t>
+          <t>1334; 7388</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1752; 10074</t>
+          <t>1655; 9707</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4390; 13336</t>
+          <t>4097; 14191</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6566; 18062</t>
+          <t>6940; 18105</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1936; 8983</t>
+          <t>1922; 9335</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7483; 21213</t>
+          <t>7921; 22069</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4849; 15464</t>
+          <t>4925; 14519</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7527; 20054</t>
+          <t>8273; 19521</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3196; 11478</t>
+          <t>3221; 11189</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5190; 17119</t>
+          <t>5014; 16868</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4692; 14804</t>
+          <t>4886; 14795</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6807; 17821</t>
+          <t>6996; 18066</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3251; 11437</t>
+          <t>3262; 11672</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3703; 13771</t>
+          <t>3723; 13517</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11499; 25294</t>
+          <t>11918; 25424</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17707; 33627</t>
+          <t>17071; 33683</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8073; 19699</t>
+          <t>8150; 20111</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>10908; 25233</t>
+          <t>10463; 25992</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP28_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP28_R-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,32 +649,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>0,58%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1,1%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,9</t>
+          <t>0,0; 2,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,32</t>
+          <t>0,49; 4,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,03</t>
+          <t>0,0; 2,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,1</t>
+          <t>0,0; 3,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -757,12 +757,12 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,91</t>
+          <t>0,0; 1,94</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,91</t>
+          <t>0,51; 2,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>1,21%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0,93%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,91</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>0,0; 1,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 1,74</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,43</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,31; 3,13</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 1,93</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
           <t>0,3; 2,51</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,52</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,92</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,21</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,78</t>
-        </is>
-      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,01</t>
+          <t>0,0; 1,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,0</t>
+          <t>0,34; 1,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,3</t>
+          <t>0,16; 1,44</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,46</t>
+          <t>0,16; 1,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,34</t>
+          <t>0,16; 1,52</t>
         </is>
       </c>
     </row>
@@ -929,49 +929,49 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1,6%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3,25%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2,04%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>1,54%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>2,53%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,31</t>
+          <t>0,48; 4,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 6,17</t>
+          <t>0,49; 4,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,15</t>
+          <t>0,39; 3,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,65</t>
+          <t>0,0; 2,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 3,99</t>
+          <t>0,51; 4,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,47</t>
+          <t>1,41; 6,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,52</t>
+          <t>0,46; 4,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>0,0; 2,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,33</t>
+          <t>0,52; 3,07</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,24</t>
+          <t>1,37; 4,51</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,38</t>
+          <t>0,83; 3,42</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,71</t>
+          <t>0,18; 1,68</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3,17%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1,67%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3,88%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0,77%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,7</t>
+          <t>0,94; 4,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,77; 6,91</t>
+          <t>1,51; 6,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,84</t>
+          <t>0,83; 4,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,39</t>
+          <t>0,49; 3,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,49</t>
+          <t>0,66; 3,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 6,09</t>
+          <t>1,7; 7,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,61</t>
+          <t>0,0; 2,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,2</t>
+          <t>1,72; 6,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,56</t>
+          <t>1,02; 3,29</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 5,61</t>
+          <t>2,06; 5,66</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,95</t>
+          <t>0,6; 2,91</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,82</t>
+          <t>1,36; 4,0</t>
         </is>
       </c>
     </row>
@@ -1209,62 +1209,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>1,32%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2,02%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,01%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>1,0%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,17</t>
+          <t>0,65; 1,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,02</t>
+          <t>0,97; 2,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,77</t>
+          <t>0,58; 1,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,55</t>
+          <t>0,52; 1,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,07</t>
+          <t>0,69; 2,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,62</t>
+          <t>1,16; 3,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,75</t>
+          <t>0,49; 1,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,78</t>
+          <t>0,84; 2,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,83</t>
+          <t>0,83; 1,81</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,52</t>
+          <t>1,34; 2,59</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,55</t>
+          <t>0,62; 1,55</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,83</t>
+          <t>0,82; 2,01</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1514,27 +1514,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1577,32 +1577,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>598</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1445</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1999</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1645,12 +1645,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3001</t>
+          <t>0; 3182</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4370</t>
+          <t>642; 5306</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1665,12 +1665,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3645</t>
+          <t>0; 3062</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>638; 5405</t>
+          <t>0; 4973</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1685,12 +1685,12 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4274</t>
+          <t>0; 4342</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1288; 7661</t>
+          <t>1342; 7251</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1359</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1455</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2991</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>756</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1751</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1359</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1455</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>666</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>492</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>1603</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>783; 7211</t>
+          <t>0; 4802</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4122</t>
+          <t>0; 4416</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>565; 4720</t>
+          <t>0; 3903</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 829</t>
+          <t>0; 3818</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4805</t>
+          <t>778; 7757</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5361</t>
+          <t>0; 4082</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3985</t>
+          <t>564; 4728</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5480</t>
+          <t>0; 2032</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1786; 9945</t>
+          <t>1672; 9194</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>706; 5893</t>
+          <t>707; 6524</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>602; 6015</t>
+          <t>665; 6075</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>320; 4587</t>
+          <t>486; 4597</t>
         </is>
       </c>
     </row>
@@ -1930,37 +1930,37 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2075</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2665</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2594</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1560</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>2029</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>4805</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>3409</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>810</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2075</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2665</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2594</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1579</t>
+          <t>705</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2389</t>
+          <t>2265</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>641; 5480</t>
+          <t>665; 5737</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2089; 9121</t>
+          <t>728; 6729</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1265; 6931</t>
+          <t>653; 6425</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4547</t>
+          <t>0; 5503</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>663; 5543</t>
+          <t>642; 5820</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>755; 6595</t>
+          <t>2090; 9714</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>648; 5929</t>
+          <t>761; 7401</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 5092</t>
+          <t>0; 3559</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1998; 8864</t>
+          <t>1394; 8169</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3978; 12537</t>
+          <t>4062; 13338</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2670; 11345</t>
+          <t>2771; 11457</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>695; 6581</t>
+          <t>659; 6258</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4738</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5300</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3402</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4362</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>3214</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>6047</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>1211</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8568</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4738</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5300</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3402</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4571</t>
+          <t>9037</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13139</t>
+          <t>13399</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1265; 7108</t>
+          <t>1942; 9445</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2764; 10770</t>
+          <t>2513; 10055</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4447</t>
+          <t>1323; 7582</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3939; 14780</t>
+          <t>1417; 9538</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2077; 9245</t>
+          <t>1268; 7137</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2465; 10169</t>
+          <t>2646; 11691</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1334; 7388</t>
+          <t>0; 4279</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1655; 9707</t>
+          <t>4388; 17067</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4097; 14191</t>
+          <t>4046; 13082</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6940; 18105</t>
+          <t>6665; 18265</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1922; 9335</t>
+          <t>1899; 9206</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7921; 22069</t>
+          <t>7447; 21835</t>
         </is>
       </c>
     </row>
@@ -2346,37 +2346,37 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>8810</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>11419</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6661</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>7033</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>8832</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>13052</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>6372</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>9542</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>8810</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>11419</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>6661</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7453</t>
+          <t>10234</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16995</t>
+          <t>17268</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4925; 14519</t>
+          <t>4679; 14251</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8273; 19521</t>
+          <t>6709; 18126</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3221; 11189</t>
+          <t>3878; 11530</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5014; 16868</t>
+          <t>3633; 12623</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4886; 14795</t>
+          <t>4603; 14566</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6996; 18066</t>
+          <t>7493; 19592</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3262; 11672</t>
+          <t>3113; 11453</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3723; 13517</t>
+          <t>5245; 17750</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11918; 25424</t>
+          <t>11480; 25050</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17071; 33683</t>
+          <t>17910; 34532</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8150; 20111</t>
+          <t>8009; 20213</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>10463; 25992</t>
+          <t>10858; 26537</t>
         </is>
       </c>
     </row>
